--- a/api/templates/all_device_report/en.xlsx
+++ b/api/templates/all_device_report/en.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="201">
   <si>
     <t xml:space="preserve">GeneXpert Devices</t>
   </si>
@@ -106,6 +106,9 @@
     <t xml:space="preserve">Total</t>
   </si>
   <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
     <t xml:space="preserve">&lt;name&gt;</t>
   </si>
   <si>
@@ -161,6 +164,9 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;totalXpertTests&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;totalOtherTests&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Inventory</t>
@@ -1137,7 +1143,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AMJ12"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="27.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="15.21"/>
@@ -1263,6 +1269,9 @@
       <c r="S9" s="8" t="s">
         <v>26</v>
       </c>
+      <c r="T9" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="AMA9" s="0"/>
       <c r="AMB9" s="0"/>
       <c r="AMC9" s="0"/>
@@ -1276,61 +1285,64 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O10" s="15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P10" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R10" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S10" s="11" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="T10" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1360,7 +1372,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I62"/>
-  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.21"/>
@@ -1374,18 +1386,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1395,7 +1407,7 @@
     </row>
     <row r="7" s="22" customFormat="true" ht="47.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>11</v>
@@ -1404,30 +1416,30 @@
         <v>13</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C8" s="25" t="n">
         <v>44767.5196064815</v>
@@ -1450,10 +1462,10 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C9" s="25" t="n">
         <v>44767.4700462963</v>
@@ -1476,10 +1488,10 @@
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C10" s="25" t="n">
         <v>44757.4942013889</v>
@@ -1502,10 +1514,10 @@
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>44764.5687731481</v>
@@ -1528,10 +1540,10 @@
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C12" s="25" t="n">
         <v>44757.5088194444</v>
@@ -1554,10 +1566,10 @@
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>44421.4506597222</v>
@@ -1580,10 +1592,10 @@
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" s="25" t="n">
         <v>44767.4393634259</v>
@@ -1606,10 +1618,10 @@
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C15" s="25" t="n">
         <v>44767.4445717593</v>
@@ -1632,10 +1644,10 @@
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C16" s="25" t="n">
         <v>44767.4584953704</v>
@@ -1658,10 +1670,10 @@
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C17" s="25" t="n">
         <v>44750.5144212963</v>
@@ -1684,10 +1696,10 @@
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C18" s="25" t="n">
         <v>44763.461875</v>
@@ -1710,10 +1722,10 @@
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C19" s="25" t="n">
         <v>44764.7684375</v>
@@ -1736,10 +1748,10 @@
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C20" s="25" t="n">
         <v>44764.3677546296</v>
@@ -1762,10 +1774,10 @@
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C21" s="25" t="n">
         <v>44763.3857986111</v>
@@ -1788,10 +1800,10 @@
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C22" s="25" t="n">
         <v>44090.5202199074</v>
@@ -1814,10 +1826,10 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C23" s="25" t="n">
         <v>44764.5050694444</v>
@@ -1840,10 +1852,10 @@
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C24" s="25" t="n">
         <v>44622.6229976852</v>
@@ -1866,10 +1878,10 @@
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C25" s="25" t="n">
         <v>44767.4350462963</v>
@@ -1892,10 +1904,10 @@
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C26" s="25" t="n">
         <v>44767.4989583333</v>
@@ -1918,10 +1930,10 @@
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C27" s="25" t="n">
         <v>44705.5175</v>
@@ -1944,10 +1956,10 @@
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C28" s="25" t="n">
         <v>44665.2380208333</v>
@@ -1970,10 +1982,10 @@
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C29" s="25" t="n">
         <v>44764.6655555556</v>
@@ -1996,10 +2008,10 @@
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C30" s="25" t="n">
         <v>44685.7503472222</v>
@@ -2022,10 +2034,10 @@
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>44762.5213078704</v>
@@ -2048,10 +2060,10 @@
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C32" s="25" t="n">
         <v>44767.4802083333</v>
@@ -2074,10 +2086,10 @@
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C33" s="25" t="n">
         <v>44764.5256134259</v>
@@ -2100,10 +2112,10 @@
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C34" s="25" t="n">
         <v>44657.4216319444</v>
@@ -2126,10 +2138,10 @@
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="23" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C35" s="25" t="n">
         <v>44600.2772800926</v>
@@ -2152,10 +2164,10 @@
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C36" s="25" t="n">
         <v>44767.4631134259</v>
@@ -2178,10 +2190,10 @@
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C37" s="25" t="n">
         <v>44764.5069212963</v>
@@ -2204,10 +2216,10 @@
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="23" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C38" s="25" t="n">
         <v>44767.2838657407</v>
@@ -2230,10 +2242,10 @@
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C39" s="25" t="n">
         <v>44755.3876157407</v>
@@ -2256,10 +2268,10 @@
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C40" s="25" t="n">
         <v>44354.5274652778</v>
@@ -2282,10 +2294,10 @@
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="23" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C41" s="25" t="n">
         <v>44368.5594097222</v>
@@ -2308,10 +2320,10 @@
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="23" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C42" s="25" t="n">
         <v>44764.4977893519</v>
@@ -2334,10 +2346,10 @@
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="23" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C43" s="25" t="n">
         <v>44763.5920601852</v>
@@ -2382,7 +2394,7 @@
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="23" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B46" s="24"/>
       <c r="C46" s="25"/>
@@ -2390,7 +2402,7 @@
         <v>12518</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F46" s="26"/>
       <c r="G46" s="27" t="n">
@@ -2404,7 +2416,7 @@
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="23" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B47" s="24"/>
       <c r="C47" s="25"/>
@@ -2412,7 +2424,7 @@
         <v>18712</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F47" s="26"/>
       <c r="G47" s="27" t="n">
@@ -2426,7 +2438,7 @@
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="23" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B48" s="24"/>
       <c r="C48" s="25"/>
@@ -2434,7 +2446,7 @@
         <v>5518</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F48" s="26"/>
       <c r="G48" s="27" t="n">
@@ -2448,7 +2460,7 @@
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="23" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B49" s="24"/>
       <c r="C49" s="25"/>
@@ -2456,7 +2468,7 @@
         <v>14828</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F49" s="26"/>
       <c r="G49" s="27" t="n">
@@ -2470,7 +2482,7 @@
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="23" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B50" s="24"/>
       <c r="C50" s="25"/>
@@ -2478,7 +2490,7 @@
         <v>7117</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F50" s="26"/>
       <c r="G50" s="27" t="n">
@@ -2492,7 +2504,7 @@
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="23" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B51" s="24"/>
       <c r="C51" s="25"/>
@@ -2500,7 +2512,7 @@
         <v>47277</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F51" s="26"/>
       <c r="G51" s="27" t="n">
@@ -2514,7 +2526,7 @@
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="23" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B52" s="24"/>
       <c r="C52" s="25"/>
@@ -2522,7 +2534,7 @@
         <v>730</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F52" s="26"/>
       <c r="G52" s="27" t="n">
@@ -2536,7 +2548,7 @@
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B53" s="24"/>
       <c r="C53" s="25"/>
@@ -2544,7 +2556,7 @@
         <v>5096</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F53" s="26"/>
       <c r="G53" s="27" t="n">
@@ -2558,7 +2570,7 @@
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="23" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B54" s="24"/>
       <c r="C54" s="25"/>
@@ -2566,7 +2578,7 @@
         <v>4747</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F54" s="26"/>
       <c r="G54" s="27" t="n">
@@ -2580,7 +2592,7 @@
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="23" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B55" s="24"/>
       <c r="C55" s="25"/>
@@ -2588,7 +2600,7 @@
         <v>14463</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F55" s="26"/>
       <c r="G55" s="27" t="n">
@@ -2602,7 +2614,7 @@
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="23" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B56" s="24"/>
       <c r="C56" s="25"/>
@@ -2610,7 +2622,7 @@
         <v>5612</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F56" s="26"/>
       <c r="G56" s="27" t="n">
@@ -2643,7 +2655,7 @@
         <v>136618</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F58" s="26"/>
       <c r="G58" s="27" t="n">
@@ -2657,13 +2669,13 @@
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B59" s="31"/>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2687,7 +2699,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AK39"/>
-  <sheetFormatPr defaultColWidth="8.63671875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.65234375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="2" style="0" width="28.5"/>
@@ -2695,7 +2707,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="20.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2736,7 +2748,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2777,7 +2789,7 @@
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2933,117 +2945,117 @@
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="32"/>
       <c r="B7" s="33" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I7" s="33" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L7" s="33" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M7" s="33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O7" s="33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="P7" s="33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q7" s="33" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="R7" s="33" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="S7" s="33" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="T7" s="33" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="U7" s="33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="V7" s="33" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="W7" s="33" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="X7" s="33" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Y7" s="33" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="Z7" s="33" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AA7" s="33" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AB7" s="33" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AC7" s="33" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AD7" s="33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AE7" s="33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AF7" s="33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG7" s="33" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AH7" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AI7" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AJ7" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AK7" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="34" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B8" s="35"/>
       <c r="C8" s="35"/>
@@ -3084,7 +3096,7 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="36" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B9" s="35"/>
       <c r="C9" s="35"/>
@@ -3125,7 +3137,7 @@
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B10" s="35"/>
       <c r="C10" s="35"/>
@@ -3166,7 +3178,7 @@
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="36" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B11" s="35"/>
       <c r="C11" s="35"/>
@@ -3207,7 +3219,7 @@
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B12" s="38" t="n">
         <f aca="false">IF(B9=0,0,B10/B9)</f>
@@ -3356,7 +3368,7 @@
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="39" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B13" s="40" t="n">
         <f aca="false">B15+B16+B17+B21+B22</f>
@@ -3505,7 +3517,7 @@
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B14" s="41" t="n">
         <f aca="false">IF(B11=0,0,B13/B11)</f>
@@ -3654,7 +3666,7 @@
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="36" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B15" s="35" t="n">
         <v>808</v>
@@ -3767,7 +3779,7 @@
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="36" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B16" s="35" t="n">
         <v>8272</v>
@@ -3880,7 +3892,7 @@
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="36" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B17" s="35" t="n">
         <v>209</v>
@@ -3993,7 +4005,7 @@
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="36" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B18" s="41" t="n">
         <f aca="false">IF(B13=0,0,B15/B13)</f>
@@ -4142,7 +4154,7 @@
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="36" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B19" s="41" t="n">
         <f aca="false">IF(B10=0,0,B15/B10)</f>
@@ -4291,7 +4303,7 @@
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="36" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B20" s="41" t="n">
         <f aca="false">IF(B13=0,0,B17/B13)</f>
@@ -4440,7 +4452,7 @@
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="36" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B21" s="35" t="n">
         <v>38</v>
@@ -4553,7 +4565,7 @@
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="37" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B22" s="42" t="n">
         <v>8</v>
@@ -4666,7 +4678,7 @@
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="39" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B23" s="40"/>
       <c r="C23" s="40"/>
@@ -4707,7 +4719,7 @@
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="36" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B24" s="41" t="n">
         <f aca="false">IF(B15=0,0,B23/B15)</f>
@@ -4856,7 +4868,7 @@
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="37" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B25" s="43" t="n">
         <f aca="false">B13/22</f>
@@ -5081,7 +5093,7 @@
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -6026,7 +6038,7 @@
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="46" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B37" s="47" t="n">
         <v>112</v>
@@ -6139,7 +6151,7 @@
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="46" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B38" s="47" t="n">
         <v>20</v>
@@ -6252,7 +6264,7 @@
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="48" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B39" s="35" t="n">
         <f aca="false">B29+B30+B31+B32+B33+B34+B35+B36+B37+B38</f>
@@ -6416,7 +6428,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultColWidth="8.63671875" defaultRowHeight="21.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.65234375" defaultRowHeight="21.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="39.21"/>
@@ -6425,13 +6437,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6439,10 +6451,10 @@
         <v>1001</v>
       </c>
       <c r="B2" s="49" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C2" s="49" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6450,10 +6462,10 @@
         <v>1002</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6461,10 +6473,10 @@
         <v>1004</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C4" s="49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6472,10 +6484,10 @@
         <v>1005</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6483,10 +6495,10 @@
         <v>1006</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6494,10 +6506,10 @@
         <v>1007</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6505,10 +6517,10 @@
         <v>1017</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6516,10 +6528,10 @@
         <v>1018</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6527,10 +6539,10 @@
         <v>2003</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6538,10 +6550,10 @@
         <v>2005</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6549,10 +6561,10 @@
         <v>2008</v>
       </c>
       <c r="B12" s="49" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6560,10 +6572,10 @@
         <v>2009</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6571,10 +6583,10 @@
         <v>2011</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6582,10 +6594,10 @@
         <v>2014</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6593,10 +6605,10 @@
         <v>2016</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C16" s="49" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6604,10 +6616,10 @@
         <v>2018</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6615,10 +6627,10 @@
         <v>2022</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6626,10 +6638,10 @@
         <v>2025</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6637,10 +6649,10 @@
         <v>2032</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6648,10 +6660,10 @@
         <v>2034</v>
       </c>
       <c r="B21" s="49" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C21" s="49" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6659,10 +6671,10 @@
         <v>2037</v>
       </c>
       <c r="B22" s="49" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6670,10 +6682,10 @@
         <v>4010</v>
       </c>
       <c r="B23" s="49" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C23" s="49" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6681,10 +6693,10 @@
         <v>4017</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C24" s="49" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6692,10 +6704,10 @@
         <v>5006</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C25" s="49" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6703,10 +6715,10 @@
         <v>5007</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6714,10 +6726,10 @@
         <v>5011</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
